--- a/jogos_2025-01-07.xlsx
+++ b/jogos_2025-01-07.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.25</v>
+        <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="P6" t="n">
         <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X6" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['45+1']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['39', '53', '90+6']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45664.69791666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.22</v>
+        <v>3.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
         <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T7" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['39', '53', '90+6']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45664.69791666666</v>
